--- a/Target_fixed.xlsx
+++ b/Target_fixed.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ack\OneDrive\Documents\enforcement report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EEBE4F-F670-4F65-AF9F-647C6BFB728F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689C5B1C-938E-4E3A-9D4F-FDBA22946508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14265" yWindow="4260" windowWidth="13350" windowHeight="11220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fixed" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Officer Name</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Designation</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
     <t>A BHAGYASREE</t>
   </si>
   <si>
@@ -61,13 +58,52 @@
   </si>
   <si>
     <t>U JAYASRI YADAV</t>
+  </si>
+  <si>
+    <t>Sl No</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>2026-11</t>
+  </si>
+  <si>
+    <t>2026-12</t>
+  </si>
+  <si>
+    <t>2027-01</t>
+  </si>
+  <si>
+    <t>2027-02</t>
+  </si>
+  <si>
+    <t>2027-03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,8 +112,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF171717"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF161616"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -109,7 +167,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -117,11 +175,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,92 +462,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1138000</v>
+      </c>
+      <c r="E2">
+        <v>1138000</v>
+      </c>
+      <c r="F2">
+        <v>1138000</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>1138000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>1138000</v>
+      </c>
+      <c r="E3">
+        <v>1138000</v>
+      </c>
+      <c r="F3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1138000</v>
+      </c>
+      <c r="E4">
+        <v>1138000</v>
+      </c>
+      <c r="F4">
+        <v>1138000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>1138000</v>
+      </c>
+      <c r="E5">
+        <v>1138000</v>
+      </c>
+      <c r="F5">
         <v>1138000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1138000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1138000</v>
+      </c>
+      <c r="E6">
+        <v>1138000</v>
+      </c>
+      <c r="F6">
         <v>1138000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1138000</v>
+      </c>
+      <c r="E7">
+        <v>1138000</v>
+      </c>
+      <c r="F7">
         <v>1138000</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Target_fixed.xlsx
+++ b/Target_fixed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ack\OneDrive\Documents\enforcement report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ack\My Drive\HINDUPUR-2022-2025\Target 2026-2027\Reports MVIs\web data files_github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689C5B1C-938E-4E3A-9D4F-FDBA22946508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF8D610-9E4F-44EC-AC2C-FD8B71F87450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14265" yWindow="4260" windowWidth="13350" windowHeight="11220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -537,6 +537,9 @@
       <c r="F2">
         <v>1138000</v>
       </c>
+      <c r="G2">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -557,6 +560,9 @@
       <c r="F3">
         <v>1138000</v>
       </c>
+      <c r="G3">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -577,6 +583,9 @@
       <c r="F4">
         <v>1138000</v>
       </c>
+      <c r="G4">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -597,6 +606,9 @@
       <c r="F5">
         <v>1138000</v>
       </c>
+      <c r="G5">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -617,6 +629,9 @@
       <c r="F6">
         <v>1138000</v>
       </c>
+      <c r="G6">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -635,6 +650,9 @@
         <v>1138000</v>
       </c>
       <c r="F7">
+        <v>1138000</v>
+      </c>
+      <c r="G7">
         <v>1138000</v>
       </c>
     </row>

--- a/Target_fixed.xlsx
+++ b/Target_fixed.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ack\My Drive\HINDUPUR-2022-2025\Target 2026-2027\Reports MVIs\web data files_github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ack\My Drive\HINDUPUR-2022-2025\Target 2026-2027\Reports MVIs\Web data files_github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF8D610-9E4F-44EC-AC2C-FD8B71F87450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D622AB-5E8A-4F5A-A14E-4CF3F4514710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -540,6 +540,9 @@
       <c r="G2">
         <v>1138000</v>
       </c>
+      <c r="H2">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -563,6 +566,9 @@
       <c r="G3">
         <v>1138000</v>
       </c>
+      <c r="H3">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -586,6 +592,9 @@
       <c r="G4">
         <v>1138000</v>
       </c>
+      <c r="H4">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -609,6 +618,9 @@
       <c r="G5">
         <v>1138000</v>
       </c>
+      <c r="H5">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -632,6 +644,9 @@
       <c r="G6">
         <v>1138000</v>
       </c>
+      <c r="H6">
+        <v>1138000</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -653,6 +668,9 @@
         <v>1138000</v>
       </c>
       <c r="G7">
+        <v>1138000</v>
+      </c>
+      <c r="H7">
         <v>1138000</v>
       </c>
     </row>
